--- a/docs/Inventario.xlsx
+++ b/docs/Inventario.xlsx
@@ -13,14 +13,14 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={9b66a56e-fffd-4eb5-84d5-6d0a41e18c8f}</author>
-    <author>tc={9fcf18bf-aa13-402f-8a32-4fd6062503e2}</author>
-    <author>tc={b3940f97-a91a-4781-add5-9bbcbae5137f}</author>
-    <author>tc={bc8aa272-b332-4289-9dee-e53f55a44d3b}</author>
-    <author>tc={dbfd2c86-1d23-43cf-bd1f-f9d1690c7894}</author>
+    <author>tc={0ff6d955-5c95-40bc-8f36-2b7f87ed9c9a}</author>
+    <author>tc={3372abb3-079f-4283-887e-878705c651f7}</author>
+    <author>tc={4f01d7cb-8516-4837-a54f-a884d7a714f6}</author>
+    <author>tc={9fae933d-bb75-4caf-ba6b-1e5c9c7ffc11}</author>
+    <author>tc={f79fcb1e-e1c2-41f4-93e8-a8ba9273584e}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{9b66a56e-fffd-4eb5-84d5-6d0a41e18c8f}" ref="B4">
+    <comment authorId="0" xr:uid="{0ff6d955-5c95-40bc-8f36-2b7f87ed9c9a}" ref="B4">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -29,7 +29,16 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{9fcf18bf-aa13-402f-8a32-4fd6062503e2}" ref="G21">
+    <comment authorId="1" xr:uid="{3372abb3-079f-4283-887e-878705c651f7}" ref="I25">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	Precio por kit
+</t>
+      </text>
+    </comment>
+    <comment authorId="2" xr:uid="{4f01d7cb-8516-4837-a54f-a884d7a714f6}" ref="G21">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -38,16 +47,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="2" xr:uid="{b3940f97-a91a-4781-add5-9bbcbae5137f}" ref="I24">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Precio por kit
-</t>
-      </text>
-    </comment>
-    <comment authorId="3" xr:uid="{bc8aa272-b332-4289-9dee-e53f55a44d3b}" ref="G23">
+    <comment authorId="3" xr:uid="{9fae933d-bb75-4caf-ba6b-1e5c9c7ffc11}" ref="G24">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -56,7 +56,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="4" xr:uid="{dbfd2c86-1d23-43cf-bd1f-f9d1690c7894}" ref="G20">
+    <comment authorId="4" xr:uid="{f79fcb1e-e1c2-41f4-93e8-a8ba9273584e}" ref="G20">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="214">
   <si>
     <t>Item</t>
   </si>
@@ -103,7 +103,7 @@
     <t>Cantidad</t>
   </si>
   <si>
-    <t>Add</t>
+    <t>Storage</t>
   </si>
   <si>
     <t>Precio U (€)</t>
@@ -463,6 +463,21 @@
     <t>Variante SHR 04V 500 mm de longitud con 4 pines Cable para conector QWIIC/QT sensor IMU (ICM 20948)</t>
   </si>
   <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>I2C Qwiic cable set Stemma QT wire for SparkFun development boards Sensor plate Breakout Breadboard 4 Pin Sh1.0 plug : Amazon.nl: Business, Industry &amp; Science</t>
+    </r>
+  </si>
+  <si>
+    <t>I2C Qwiic cable set Stemma QT wire for SparkFun development boards Sensor plate Breakout Breadboard 4 Pin Sh1.0 plug - Contains 12 cables in different lengths and styles (10cm, 20cm, 30cm, 50cm. SH1.0 plug and plugboard jumper and bush bridge)</t>
+  </si>
+  <si>
     <t>Cable AWG24 4 Core Shielded</t>
   </si>
   <si>
@@ -505,7 +520,7 @@
     <t>Herramienta</t>
   </si>
   <si>
-    <t>Weller WE 1010 70W/230V</t>
+    <t>WE 1010 70W/230V</t>
   </si>
   <si>
     <t>Weller</t>
@@ -526,19 +541,7 @@
     <t>Estacion de soldadura Weller</t>
   </si>
   <si>
-    <t>WSW SCN M1</t>
-  </si>
-  <si>
-    <t>T0051402799</t>
-  </si>
-  <si>
-    <t>Weller WSW SCN M1 (T0051402899) Alambre De Soldadura Sin Plomo, Ø 0,3 Mm, Aleación Sn99.3Cu0.6Ni0.05, Contenido De Fundente 3.5%, 100g : Amazon.es: Bricolaje y herramientas</t>
-  </si>
-  <si>
-    <t>Alambre para soldar Nucleo Flux sin Plomo (Welding Wire without Lead) Alloy Sn99.3Cu0.6Ni0.05, Flux Content 3.5%, Punto de fusión: aprox. 228–229 °C, Ø 0.3 mm, Ø 0.5 mm, Ø 1.0 mm, 100g</t>
-  </si>
-  <si>
-    <t>KIT for WE 1010</t>
+    <t>KIT 5 Puntas for WE 1010</t>
   </si>
   <si>
     <r>
@@ -553,7 +556,193 @@
     <t>Juego de 5 Puntas de Soldadura: ETA 1,6mm ETB de 2,4 mm ETC de 3,18 mm ETP de 0,8 mm TETS de 0,4 mm para la Estación de Soldadura WE1010</t>
   </si>
   <si>
+    <t>Manual Desoldering 7874B</t>
+  </si>
+  <si>
+    <t>7874B</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>Weller 7874B Manual ESD Safe Desoldering Pump With Aluminum Body, Blue : Amazon.nl: DIY &amp; Tools</t>
+    </r>
+  </si>
+  <si>
+    <t>Manual ESD Safe Desoldering Pump With Aluminum Body</t>
+  </si>
+  <si>
     <t>Helping Hands 4 Magnetic Flexible</t>
+  </si>
+  <si>
+    <t>WALCCHHM-02EU</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>Weller WLACCHHM-02EU hand help with 4 movable and adjustable magnetic arms for multiple configurations : Amazon.nl: DIY &amp; Tools</t>
+    </r>
+  </si>
+  <si>
+    <t>Hand help with 4 movable and adjustable magnetic arms for multiple configurations</t>
+  </si>
+  <si>
+    <t>WSW SCN M1</t>
+  </si>
+  <si>
+    <t>T0051402799</t>
+  </si>
+  <si>
+    <t>Weller WSW SCN M1 (T0051402899) Alambre De Soldadura Sin Plomo, Ø 0,3 Mm, Aleación Sn99.3Cu0.6Ni0.05, Contenido De Fundente 3.5%, 100g : Amazon.es: Bricolaje y herramientas</t>
+  </si>
+  <si>
+    <t>Alambre para soldar Nucleo Flux sin Plomo (Welding Wire without Lead) Alloy Sn99.3Cu0.6Ni0.05, Flux Content 3.5%, Punto de fusión: aprox. 228–229 °C, Ø 0.3 mm, 100g</t>
+  </si>
+  <si>
+    <t>WSW SAC L0</t>
+  </si>
+  <si>
+    <t>T0051388799</t>
+  </si>
+  <si>
+    <t>Weller WSW SAC L0 Soldeertin, loodvrij Spoel Sn3,0Ag0,5Cu 250 g 0.8 mm kopen ? Conrad Electronic</t>
+  </si>
+  <si>
+    <t>Alambre para soldar Nucleo Flux sin Plomo (Welding Wire without Lead) Alloy Sn96.5Ag3.0Cu0.5, Flux Content 3.5%, Punto de fusión: aprox. 216–218 °C, Ø 0.8 mm, 250g</t>
+  </si>
+  <si>
+    <t>Limpieza</t>
+  </si>
+  <si>
+    <t>TC205</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>Weller TC205 kopen ? Conrad Electronic</t>
+    </r>
+  </si>
+  <si>
+    <t>Esponja reemplazo para Estacion de soldadura Weller</t>
+  </si>
+  <si>
+    <t>WLACCBS-02 Brass Sponge</t>
+  </si>
+  <si>
+    <t>T0051384099</t>
+  </si>
+  <si>
+    <t>Weller WLACCBS-02 Esponja de Latón para Limpiar Las Puntas de Soldadura : Amazon.es</t>
+  </si>
+  <si>
+    <t>Lana metálica de repuesto de latón, juego de 5 piezas</t>
+  </si>
+  <si>
+    <t>ISO-Flux "E" Soldeerpasta 50g</t>
+  </si>
+  <si>
+    <t>Felder</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>Felder ISO-Flux "E" Soldeerpasta Inhoud 1 stuk(s) kopen ? Conrad Electronic</t>
+    </r>
+  </si>
+  <si>
+    <t>Flux: ROM1 (EN 61190-1-1/ J-STD-004), 1123 (ISO 9454-1:2016), Contenido halógeno: &lt; 1%, Contenido de sólidos: 25%, Densidad (20 °C): 0,850 g/cm³, 50g</t>
+  </si>
+  <si>
+    <t>ZD-180 Desoldering Wire Flux soaked</t>
+  </si>
+  <si>
+    <t>TOOLCRAFT</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>TOOLCRAFT ZD-180 Desoldering Wire Length 1.5 m Width 3.0 mm Want to buy flux soaked? Conrad Electronic</t>
+    </r>
+  </si>
+  <si>
+    <t>Length 1.5 m Width 3.0 mm</t>
+  </si>
+  <si>
+    <t>ECO-301 - Alcohol Isopropílico 99,9%</t>
+  </si>
+  <si>
+    <t>EQM</t>
+  </si>
+  <si>
+    <t>ECO-301</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>EQM - ECO-301 - Alcohol Isopropílico 99,9% - 1L - Isopropanol - Limpieza componentes electrónicos, objetivos y pantallas - Limpieza de resinas en impresión 3D - Limpiacristales y desengrasante : Amazon.es: Salud y cuidado personal</t>
+    </r>
+  </si>
+  <si>
+    <t>Isopropanol - Limpieza componentes electrónicos, objetivos y pantallas - Limpieza de resinas en impresión 3D - Limpiacristales y desengrasante ECO-301 - 1L</t>
+  </si>
+  <si>
+    <t>Isopropanol 99.9% Cleaner</t>
+  </si>
+  <si>
+    <t>Nanoprotect</t>
+  </si>
+  <si>
+    <t>Iso-1x1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>Nanoprotect Isopropanol 99.9% | 1 Litre Cleaner, High Percentage Isopropyl Alcohol | IPA Cleaning Alcohol for Home and Electronics | Made in Germany : Amazon.nl: Health &amp; Personal Care</t>
+    </r>
+  </si>
+  <si>
+    <t>IPA Cleaning Alcohol for Home and Electronics - 1L</t>
+  </si>
+  <si>
+    <t>Tip Tinner 30g</t>
+  </si>
+  <si>
+    <t>6-30g Soldering Iron Tip Cleaning Paste Soldering Iron Tip Tinner Activator Tip Cleaner Remover BGA Refresher Repair Tools - AliExpress 1420</t>
+  </si>
+  <si>
+    <t>Soldering Iron Tip Cleaning Paste Soldering Iron Tip Tinner Activator Tip Cleaner Remover BGA Refresher Repair Tools, 30g</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>Welding Magnifying Glass LED Light Auxiliary Clip loupe Magnifier 3 In1 Hand Soldering Solder Iron Stand Holder Station - AliExpress 1420</t>
+    </r>
+  </si>
+  <si>
+    <t>Product D Specifications: Material: ABS, Color: Black, Mirror Diameter: 72mm (large lens), 30mm (small lens), 22mm (small lens), Magnification: 3 times (large lens), 25 times (small lens), 4.5 times (small lens), Battery: 3 *AAA button battery (not included), Light Source: 10 Led Lights, USB Power: USB Cable Included, Item Size: 235 * 190 * 86mm / 9.25 * 7.48 * 3.39in</t>
   </si>
   <si>
     <t>TLH-D10-4</t>
@@ -613,6 +802,9 @@
     <t>Count smart multimeter, voltmeter, multimeter, tester for AC/DC current, AC/DC voltage, temperature, resistance, frequency, capacity, continuity, test diodes</t>
   </si>
   <si>
+    <t>Alimentacion</t>
+  </si>
+  <si>
     <t>TPS3010 30V 10A</t>
   </si>
   <si>
@@ -632,6 +824,51 @@
   </si>
   <si>
     <t>Fuente de laboratorio 30V 10A con USB 18W y Type-C 18W</t>
+  </si>
+  <si>
+    <t>Celda Samsung 30T 21700</t>
+  </si>
+  <si>
+    <t>Samsung</t>
+  </si>
+  <si>
+    <t>30T</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>3000mAh, 3.6V nominal, 4.2V cargada, 2.5V cutoff, descarga máxima continua 35A</t>
+  </si>
+  <si>
+    <t>Celda Samsung 20S 18650</t>
+  </si>
+  <si>
+    <t>20S</t>
+  </si>
+  <si>
+    <t>2000mAh, 3.6V nominal, 4.2V cargada, 2.5V cutoff, descarga máxima continua 30A</t>
+  </si>
+  <si>
+    <t>PB2SL 18650/21700</t>
+  </si>
+  <si>
+    <t>XTAR</t>
+  </si>
+  <si>
+    <t>PB2SL</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>XTAR PB2SL V2 18650/21700 Battery Charger &amp; Power Bank Fast Charging Smart Management Dual Function Safe Portable Solution - AliExpress</t>
+    </r>
+  </si>
+  <si>
+    <t>Datasheet del V1 (posiblemente no se consiga y toque el V2). Input (entrada): QC3.0 &amp; PD3.0, 5V ⎓ 2A, 9V ⎓ 2A, 12V ⎓ 1.5A, Corriente de carga constante: 2A ×2, 2A ×1, 1A ×2 Salida USB-A: QC3.0 / QC2.0 / FCP / PE2.0 / PE1.1 / SFCP Salida USB-C: PD3.0 / PD2.0 / QC3.0 / QC2.0 / FCP / PE2.0 / PE1.1 / SFCP Voltaje de corte de carga: 4.2 ± 0.05V Corriente de corte: ≤120 mA Temperatura de operación: 0–40 °C Dimensiones: 125 × 58 × 28 mm Peso: 85 g</t>
   </si>
   <si>
     <t>Chaqueta</t>
@@ -822,7 +1059,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Izaya JL (Izaya JL)" id="{38d3f8a4-9c09-41a3-9ff6-94650df417db}" providerId="google-sheets"/>
+  <x18tc:person displayName="Izaya JL (Izaya JL)" id="{881a7544-1cad-4a93-ac90-3765a5a655b8}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -1022,19 +1259,19 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="G21" dT="2026-01-27T20:09:02.00" personId="{38d3f8a4-9c09-41a3-9ff6-94650df417db}" id="{9fcf18bf-aa13-402f-8a32-4fd6062503e2}" done="0">
+  <x18tc:threadedComment ref="G21" dT="2026-01-27T20:09:02.00" personId="{881a7544-1cad-4a93-ac90-3765a5a655b8}" id="{4f01d7cb-8516-4837-a54f-a884d7a714f6}" done="0">
     <x18tc:text xml:space="preserve">50 Metros</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="I24" dT="2026-01-27T20:08:33.00" personId="{38d3f8a4-9c09-41a3-9ff6-94650df417db}" id="{b3940f97-a91a-4781-add5-9bbcbae5137f}" done="0">
+  <x18tc:threadedComment ref="I25" dT="2026-01-27T20:08:33.00" personId="{881a7544-1cad-4a93-ac90-3765a5a655b8}" id="{3372abb3-079f-4283-887e-878705c651f7}" done="0">
     <x18tc:text xml:space="preserve">Precio por kit</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="G23" dT="2026-01-27T20:09:30.00" personId="{38d3f8a4-9c09-41a3-9ff6-94650df417db}" id="{bc8aa272-b332-4289-9dee-e53f55a44d3b}" done="0">
+  <x18tc:threadedComment ref="G24" dT="2026-01-27T20:09:30.00" personId="{881a7544-1cad-4a93-ac90-3765a5a655b8}" id="{9fae933d-bb75-4caf-ba6b-1e5c9c7ffc11}" done="0">
     <x18tc:text xml:space="preserve">5 Metros</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="B4" dT="2026-02-28T16:20:37.00" personId="{38d3f8a4-9c09-41a3-9ff6-94650df417db}" id="{9b66a56e-fffd-4eb5-84d5-6d0a41e18c8f}" done="0">
+  <x18tc:threadedComment ref="B4" dT="2026-02-28T16:20:37.00" personId="{881a7544-1cad-4a93-ac90-3765a5a655b8}" id="{0ff6d955-5c95-40bc-8f36-2b7f87ed9c9a}" done="0">
     <x18tc:text xml:space="preserve">Es una opción si quieren usar antena externa</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="G20" dT="2026-01-29T20:25:19.00" personId="{38d3f8a4-9c09-41a3-9ff6-94650df417db}" id="{dbfd2c86-1d23-43cf-bd1f-f9d1690c7894}" done="0">
+  <x18tc:threadedComment ref="G20" dT="2026-01-29T20:25:19.00" personId="{881a7544-1cad-4a93-ac90-3765a5a655b8}" id="{f79fcb1e-e1c2-41f4-93e8-a8ba9273584e}" done="0">
     <x18tc:text xml:space="preserve">20x 2p female housing
 20x 2p male plug
 20x 3p female housing
@@ -1064,7 +1301,7 @@
     <col customWidth="1" min="5" max="5" width="15.25"/>
     <col customWidth="1" min="6" max="6" width="57.88"/>
     <col customWidth="1" min="7" max="7" width="8.5"/>
-    <col customWidth="1" min="8" max="8" width="4.25"/>
+    <col customWidth="1" min="8" max="8" width="7.25"/>
     <col customWidth="1" min="9" max="9" width="10.25"/>
     <col customWidth="1" min="10" max="10" width="12.88"/>
     <col customWidth="1" min="11" max="11" width="162.38"/>
@@ -1134,7 +1371,7 @@
         <v>12.6</v>
       </c>
       <c r="J2" s="7">
-        <f t="shared" ref="J2:J32" si="1">SUM(G2:H2)*I2</f>
+        <f t="shared" ref="J2:J47" si="1">SUM(G2:H2)*I2</f>
         <v>63</v>
       </c>
       <c r="K2" s="4" t="s">
@@ -1383,11 +1620,11 @@
         <v>3.0</v>
       </c>
       <c r="I9" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="J9" s="7">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>47</v>
@@ -1865,32 +2102,32 @@
         <v>95</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="E23" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F23" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>106</v>
-      </c>
       <c r="G23" s="4">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="H23" s="4">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="I23" s="7">
-        <v>9.0</v>
+        <v>2.75</v>
       </c>
       <c r="J23" s="7">
         <f t="shared" si="1"/>
-        <v>45</v>
+        <v>27.5</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24">
@@ -1898,35 +2135,35 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="F24" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="G24" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H24" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="I24" s="7">
+        <v>9.0</v>
+      </c>
+      <c r="J24" s="7">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="K24" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="G24" s="12">
-        <v>3.0</v>
-      </c>
-      <c r="H24" s="12">
-        <v>6.0</v>
-      </c>
-      <c r="I24" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="J24" s="13">
-        <f t="shared" si="1"/>
-        <v>27</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="25">
@@ -1934,35 +2171,35 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="F25" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="G25" s="12">
+        <v>3.0</v>
+      </c>
+      <c r="H25" s="12">
+        <v>6.0</v>
+      </c>
+      <c r="I25" s="13">
+        <v>3.0</v>
+      </c>
+      <c r="J25" s="13">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="K25" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="G25" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="H25" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="I25" s="7">
-        <v>159.0</v>
-      </c>
-      <c r="J25" s="7">
-        <f t="shared" si="1"/>
-        <v>159</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="26">
@@ -1970,19 +2207,19 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E26" s="5" t="s">
+      <c r="F26" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>122</v>
       </c>
       <c r="G26" s="4">
         <v>1.0</v>
@@ -1991,14 +2228,14 @@
         <v>0.0</v>
       </c>
       <c r="I26" s="7">
-        <v>36.0</v>
+        <v>159.0</v>
       </c>
       <c r="J26" s="7">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>159</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27">
@@ -2006,19 +2243,19 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C27" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F27" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="G27" s="4">
         <v>1.0</v>
@@ -2034,7 +2271,7 @@
         <v>22</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28">
@@ -2042,35 +2279,35 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C28" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E28" s="5" t="s">
+      <c r="F28" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="G28" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H28" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I28" s="7">
+        <v>17.0</v>
+      </c>
+      <c r="J28" s="7">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="K28" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="G28" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="H28" s="12">
-        <v>0.0</v>
-      </c>
-      <c r="I28" s="13">
-        <v>7.0</v>
-      </c>
-      <c r="J28" s="13">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="K28" s="11" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="29">
@@ -2078,19 +2315,19 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C29" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="F29" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="G29" s="4">
         <v>1.0</v>
@@ -2099,14 +2336,14 @@
         <v>0.0</v>
       </c>
       <c r="I29" s="7">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="J29" s="7">
         <f t="shared" si="1"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30">
@@ -2114,35 +2351,35 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C30" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F30" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="G30" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H30" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I30" s="7">
+        <v>36.0</v>
+      </c>
+      <c r="J30" s="7">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="K30" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="G30" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="H30" s="12">
-        <v>0.0</v>
-      </c>
-      <c r="I30" s="13">
-        <v>59.0</v>
-      </c>
-      <c r="J30" s="13">
-        <f t="shared" si="1"/>
-        <v>59</v>
-      </c>
-      <c r="K30" s="11" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="31">
@@ -2150,19 +2387,19 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>144</v>
+        <v>139</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>140</v>
       </c>
       <c r="G31" s="4">
         <v>1.0</v>
@@ -2171,14 +2408,14 @@
         <v>0.0</v>
       </c>
       <c r="I31" s="7">
-        <v>45.0</v>
+        <v>62.0</v>
       </c>
       <c r="J31" s="7">
         <f t="shared" si="1"/>
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32">
@@ -2186,153 +2423,603 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="G32" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H32" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="I32" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="J32" s="7">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3">
+        <v>32.0</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="D33" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="F33" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="G33" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H33" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="I33" s="7">
+        <v>13.0</v>
+      </c>
+      <c r="J33" s="7">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="K33" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="F32" s="6" t="s">
+    </row>
+    <row r="34">
+      <c r="A34" s="3">
+        <v>33.0</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="G32" s="12">
+      <c r="D34" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E34" s="5">
+        <v>2.5280035E7</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="G34" s="4">
         <v>1.0</v>
       </c>
-      <c r="H32" s="12">
+      <c r="H34" s="4">
         <v>0.0</v>
       </c>
-      <c r="I32" s="13">
+      <c r="I34" s="7">
+        <v>8.0</v>
+      </c>
+      <c r="J34" s="7">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3">
+        <v>34.0</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E35" s="5">
+        <v>1013274.0</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G35" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H35" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="I35" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="J35" s="7">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3">
+        <v>35.0</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="G36" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H36" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I36" s="7">
+        <v>9.0</v>
+      </c>
+      <c r="J36" s="7">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3">
+        <v>36.0</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="G37" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H37" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I37" s="7">
+        <v>10.0</v>
+      </c>
+      <c r="J37" s="7">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3">
+        <v>37.0</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="G38" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H38" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I38" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="J38" s="7">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3">
+        <v>38.0</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="G39" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H39" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I39" s="7">
+        <v>17.0</v>
+      </c>
+      <c r="J39" s="7">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3">
+        <v>39.0</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="G40" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="H40" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="I40" s="13">
+        <v>7.0</v>
+      </c>
+      <c r="J40" s="13">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3">
+        <v>40.0</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="G41" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H41" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I41" s="7">
+        <v>46.0</v>
+      </c>
+      <c r="J41" s="7">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3">
+        <v>41.0</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G42" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="H42" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="I42" s="13">
+        <v>59.0</v>
+      </c>
+      <c r="J42" s="13">
+        <f t="shared" si="1"/>
+        <v>59</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3">
+        <v>42.0</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="G43" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H43" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I43" s="7">
+        <v>45.0</v>
+      </c>
+      <c r="J43" s="7">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3">
+        <v>43.0</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G44" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="H44" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="I44" s="7">
+        <v>6.0</v>
+      </c>
+      <c r="J44" s="7">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3">
+        <v>44.0</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G45" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="H45" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I45" s="7">
+        <v>6.0</v>
+      </c>
+      <c r="J45" s="7">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3">
+        <v>45.0</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="G46" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="H46" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I46" s="7">
+        <v>25.0</v>
+      </c>
+      <c r="J46" s="7">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3">
+        <v>46.0</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="G47" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="H47" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="I47" s="13">
         <v>56.0</v>
       </c>
-      <c r="J32" s="13">
+      <c r="J47" s="13">
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
-      <c r="K32" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="17"/>
-      <c r="G33" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="I33" s="18">
-        <f>SUM(I2:I32)</f>
-        <v>692.7146</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="17"/>
-      <c r="E34" s="19"/>
-      <c r="G34" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="I34" s="18">
-        <f>SUM(J2:J32)</f>
-        <v>929.25</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="17"/>
-      <c r="C35" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="E35" s="19"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="17"/>
-      <c r="E36" s="19"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="20"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="17"/>
-      <c r="E37" s="19"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="17"/>
-      <c r="E38" s="19"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="20"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="17"/>
-      <c r="E39" s="19"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="20"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="17"/>
-      <c r="E40" s="19"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="20"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="17"/>
-      <c r="E41" s="19"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="17"/>
-      <c r="E42" s="19"/>
-      <c r="I42" s="20"/>
-      <c r="J42" s="20"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="17"/>
-      <c r="E43" s="19"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="17"/>
-      <c r="E44" s="19"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="17"/>
-      <c r="E45" s="19"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="20"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="17"/>
-      <c r="E46" s="19"/>
-      <c r="I46" s="20"/>
-      <c r="J46" s="20"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="17"/>
-      <c r="E47" s="19"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="20"/>
+      <c r="K47" s="4" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="17"/>
-      <c r="E48" s="19"/>
-      <c r="I48" s="20"/>
-      <c r="J48" s="20"/>
+      <c r="G48" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="I48" s="18">
+        <f>SUM(I2:I47)</f>
+        <v>923.4646</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="17"/>
       <c r="E49" s="19"/>
-      <c r="I49" s="20"/>
-      <c r="J49" s="20"/>
+      <c r="G49" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="I49" s="18">
+        <f>SUM(J2:J47)</f>
+        <v>1219.75</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="17"/>
+      <c r="C50" s="4" t="s">
+        <v>213</v>
+      </c>
       <c r="E50" s="19"/>
       <c r="I50" s="20"/>
       <c r="J50" s="20"/>
@@ -8061,13 +8748,103 @@
       <c r="I1004" s="20"/>
       <c r="J1004" s="20"/>
     </row>
+    <row r="1005">
+      <c r="A1005" s="17"/>
+      <c r="E1005" s="19"/>
+      <c r="I1005" s="20"/>
+      <c r="J1005" s="20"/>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="17"/>
+      <c r="E1006" s="19"/>
+      <c r="I1006" s="20"/>
+      <c r="J1006" s="20"/>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="17"/>
+      <c r="E1007" s="19"/>
+      <c r="I1007" s="20"/>
+      <c r="J1007" s="20"/>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="17"/>
+      <c r="E1008" s="19"/>
+      <c r="I1008" s="20"/>
+      <c r="J1008" s="20"/>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="17"/>
+      <c r="E1009" s="19"/>
+      <c r="I1009" s="20"/>
+      <c r="J1009" s="20"/>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="17"/>
+      <c r="E1010" s="19"/>
+      <c r="I1010" s="20"/>
+      <c r="J1010" s="20"/>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="17"/>
+      <c r="E1011" s="19"/>
+      <c r="I1011" s="20"/>
+      <c r="J1011" s="20"/>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="17"/>
+      <c r="E1012" s="19"/>
+      <c r="I1012" s="20"/>
+      <c r="J1012" s="20"/>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="17"/>
+      <c r="E1013" s="19"/>
+      <c r="I1013" s="20"/>
+      <c r="J1013" s="20"/>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="17"/>
+      <c r="E1014" s="19"/>
+      <c r="I1014" s="20"/>
+      <c r="J1014" s="20"/>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="17"/>
+      <c r="E1015" s="19"/>
+      <c r="I1015" s="20"/>
+      <c r="J1015" s="20"/>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="17"/>
+      <c r="E1016" s="19"/>
+      <c r="I1016" s="20"/>
+      <c r="J1016" s="20"/>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="17"/>
+      <c r="E1017" s="19"/>
+      <c r="I1017" s="20"/>
+      <c r="J1017" s="20"/>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="17"/>
+      <c r="E1018" s="19"/>
+      <c r="I1018" s="20"/>
+      <c r="J1018" s="20"/>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="17"/>
+      <c r="E1019" s="19"/>
+      <c r="I1019" s="20"/>
+      <c r="J1019" s="20"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="G50:H50"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId4" ref="F2"/>
@@ -8099,8 +8876,21 @@
     <hyperlink r:id="rId30" ref="F30"/>
     <hyperlink r:id="rId31" ref="F31"/>
     <hyperlink r:id="rId32" ref="F32"/>
+    <hyperlink r:id="rId33" ref="F33"/>
+    <hyperlink r:id="rId34" ref="F34"/>
+    <hyperlink r:id="rId35" ref="F35"/>
+    <hyperlink r:id="rId36" ref="F36"/>
+    <hyperlink r:id="rId37" ref="F37"/>
+    <hyperlink r:id="rId38" ref="F38"/>
+    <hyperlink r:id="rId39" location="nav-specification" ref="F39"/>
+    <hyperlink r:id="rId40" ref="F40"/>
+    <hyperlink r:id="rId41" ref="F41"/>
+    <hyperlink r:id="rId42" ref="F42"/>
+    <hyperlink r:id="rId43" ref="F43"/>
+    <hyperlink r:id="rId44" ref="F46"/>
+    <hyperlink r:id="rId45" ref="F47"/>
   </hyperlinks>
-  <drawing r:id="rId33"/>
-  <legacyDrawing r:id="rId34"/>
+  <drawing r:id="rId46"/>
+  <legacyDrawing r:id="rId47"/>
 </worksheet>
 </file>